--- a/01_Data/02_Processed/Datos_hojas_excel_COL/18_nodos/04_Aportes/AporCaudal_Jul26.xlsx
+++ b/01_Data/02_Processed/Datos_hojas_excel_COL/18_nodos/04_Aportes/AporCaudal_Jul26.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\My Drive\2. Universidad Nacional de Colombia\2. Postgraduate\1_SEMESTER\TESIS DE MAESTRIA\2nd Search\04_TESIS_DANIEL\03_CODIGO_TRABAJO_DANIEL\BESS_FACTS_master\01_Data\02_Processed\Datos_hojas_excel_COL\18_nodos\03_Hidraulicos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\My Drive\2. Universidad Nacional de Colombia\2. Postgraduate\1_SEMESTER\TESIS DE MAESTRIA\2nd Search\04_TESIS_DANIEL\03_CODIGO_TRABAJO_DANIEL\BESS_FACTS_master\01_Data\02_Processed\Datos_hojas_excel_COL\18_nodos\04_Aportes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E29481EE-584E-4AB7-93FB-4C6111266F7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B881037-BE2B-4CC8-A2D8-8F5D1BA8DFDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="780" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_LEEME" sheetId="1" r:id="rId1"/>
     <sheet name="01_SERIE" sheetId="2" r:id="rId2"/>
     <sheet name="02_POR_ENTIDAD" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_POR_ENTIDAD'!$A$1:$AQ$32</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -35,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2693" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2693" uniqueCount="103">
   <si>
     <t>Campo</t>
   </si>
@@ -321,6 +324,30 @@
   <si>
     <t>Tuesday</t>
   </si>
+  <si>
+    <t>URRA</t>
+  </si>
+  <si>
+    <t>PORCE II</t>
+  </si>
+  <si>
+    <t>CHIVOR</t>
+  </si>
+  <si>
+    <t>SALVAJINA</t>
+  </si>
+  <si>
+    <t>BETANIA</t>
+  </si>
+  <si>
+    <t>RIOGRANDE2</t>
+  </si>
+  <si>
+    <t>SAN LORENZO</t>
+  </si>
+  <si>
+    <t>ALTO ANCHICAYA</t>
+  </si>
 </sst>
 </file>
 
@@ -329,7 +356,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -337,13 +364,37 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -355,14 +406,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -30830,6 +30887,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AQ32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -30840,20 +30898,20 @@
       <c r="A1" t="s">
         <v>40</v>
       </c>
-      <c r="B1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="B1" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E1" t="s">
         <v>50</v>
       </c>
-      <c r="F1" t="s">
-        <v>51</v>
+      <c r="F1" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="G1" t="s">
         <v>52</v>
@@ -30861,17 +30919,17 @@
       <c r="H1" t="s">
         <v>53</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>54</v>
       </c>
       <c r="J1" t="s">
         <v>55</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L1" t="s">
-        <v>57</v>
+      <c r="L1" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="M1" t="s">
         <v>58</v>
@@ -30882,14 +30940,14 @@
       <c r="O1" t="s">
         <v>60</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="2" t="s">
         <v>61</v>
       </c>
       <c r="Q1" t="s">
         <v>62</v>
       </c>
-      <c r="R1" t="s">
-        <v>63</v>
+      <c r="R1" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="S1" t="s">
         <v>64</v>
@@ -30906,68 +30964,68 @@
       <c r="W1" t="s">
         <v>68</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>70</v>
       </c>
       <c r="Z1" t="s">
         <v>71</v>
       </c>
-      <c r="AA1" t="s">
-        <v>72</v>
+      <c r="AA1" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="AB1" t="s">
         <v>73</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>77</v>
       </c>
       <c r="AG1" t="s">
         <v>78</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="AI1" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ1" t="s">
+      <c r="AI1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AK1" s="2" t="s">
         <v>82</v>
       </c>
       <c r="AL1" t="s">
         <v>83</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AM1" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AN1" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AO1" t="s">
-        <v>86</v>
-      </c>
-      <c r="AP1" t="s">
+      <c r="AO1" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AP1" s="2" t="s">
         <v>87</v>
       </c>
       <c r="AQ1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46204</v>
       </c>
@@ -31098,7 +31156,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46205</v>
       </c>
@@ -31229,7 +31287,7 @@
         <v>2.19</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46206</v>
       </c>
@@ -31360,7 +31418,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46207</v>
       </c>
@@ -31491,7 +31549,7 @@
         <v>1.62</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46208</v>
       </c>
@@ -31622,7 +31680,7 @@
         <v>2.5499999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46209</v>
       </c>
@@ -31753,7 +31811,7 @@
         <v>2.57</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46210</v>
       </c>
@@ -32015,7 +32073,7 @@
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46212</v>
       </c>
@@ -32146,7 +32204,7 @@
         <v>2.62</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46213</v>
       </c>
@@ -32277,7 +32335,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46214</v>
       </c>
@@ -32408,7 +32466,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46215</v>
       </c>
@@ -32539,7 +32597,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46216</v>
       </c>
@@ -32670,7 +32728,7 @@
         <v>1.73</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46217</v>
       </c>
@@ -32801,7 +32859,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46218</v>
       </c>
@@ -32932,7 +32990,7 @@
         <v>1.51</v>
       </c>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46219</v>
       </c>
@@ -33063,7 +33121,7 @@
         <v>2.3199999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46220</v>
       </c>
@@ -33194,7 +33252,7 @@
         <v>3.87</v>
       </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46221</v>
       </c>
@@ -33325,7 +33383,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46222</v>
       </c>
@@ -33456,7 +33514,7 @@
         <v>3.61</v>
       </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46223</v>
       </c>
@@ -33587,7 +33645,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46224</v>
       </c>
@@ -33718,7 +33776,7 @@
         <v>1.87</v>
       </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46225</v>
       </c>
@@ -33849,7 +33907,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46226</v>
       </c>
@@ -33980,7 +34038,7 @@
         <v>8.35</v>
       </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46227</v>
       </c>
@@ -34111,7 +34169,7 @@
         <v>8.51</v>
       </c>
     </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46228</v>
       </c>
@@ -34242,7 +34300,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46229</v>
       </c>
@@ -34373,7 +34431,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46230</v>
       </c>
@@ -34504,7 +34562,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46231</v>
       </c>
@@ -34635,7 +34693,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46232</v>
       </c>
@@ -34766,7 +34824,7 @@
         <v>1.87</v>
       </c>
     </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46233</v>
       </c>
@@ -34897,7 +34955,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>46234</v>
       </c>
@@ -35029,6 +35087,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AQ32" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <dateGroupItem year="2026" month="7" day="8" dateTimeGrouping="day"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>